--- a/data/trans_orig/P37A$vacunaempresa-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunaempresa-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15809</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>679083</t>
+          <t>678203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>691832</t>
+          <t>691704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>677776</t>
+          <t>677833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686501</t>
+          <t>686483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1360538</t>
+          <t>1361377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1376722</t>
+          <t>1376545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>942029</t>
+          <t>942662</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>955636</t>
+          <t>955682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>955623</t>
+          <t>955207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965472</t>
+          <t>965517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1902717</t>
+          <t>1902888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1919575</t>
+          <t>1920267</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666540</t>
+          <t>667858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>676485</t>
+          <t>676763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673902</t>
+          <t>674330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682908</t>
+          <t>682867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1346176</t>
+          <t>1345296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1357655</t>
+          <t>1357730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>23947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923086</t>
+          <t>923700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936024</t>
+          <t>936114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1029608</t>
+          <t>1029754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1037632</t>
+          <t>1037634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1957630</t>
+          <t>1956887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972335</t>
+          <t>1971989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3228529</t>
+          <t>3227976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3252273</t>
+          <t>3251959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3350808</t>
+          <t>3351025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3367600</t>
+          <t>3368201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6589696</t>
+          <t>6587602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6616458</t>
+          <t>6616527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14717</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>20254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>688950</t>
+          <t>688752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701324</t>
+          <t>701468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685353</t>
+          <t>685752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>695919</t>
+          <t>695694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1380640</t>
+          <t>1380265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1395413</t>
+          <t>1395235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996102</t>
+          <t>995804</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011965</t>
+          <t>1011948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012925</t>
+          <t>1012882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1027214</t>
+          <t>1027246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2016321</t>
+          <t>2015423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036528</t>
+          <t>2037100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739620</t>
+          <t>741399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754480</t>
+          <t>754566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>757660</t>
+          <t>756929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>772356</t>
+          <t>772336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505505</t>
+          <t>1505949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524815</t>
+          <t>1525506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>33463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,74 +3724,74 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6331</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13918</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>27591</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>18577</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>40507</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6331</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2578</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13550</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>27591</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>18542</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>41391</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914819</t>
+          <t>914276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934686</t>
+          <t>934510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,77 +3837,77 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1045570</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1037983</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1049346</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1972049</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1959133</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1981063</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1045570</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1038351</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1049323</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1972049</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1958249</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1981098</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>64513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60565</t>
+          <t>61116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98393</t>
+          <t>100264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3362232</t>
+          <t>3362266</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3392162</t>
+          <t>3392031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3514418</t>
+          <t>3513753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3536764</t>
+          <t>3537520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6886695</t>
+          <t>6884824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6924523</t>
+          <t>6923972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664708</t>
+          <t>664972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673802</t>
+          <t>673800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>666155</t>
+          <t>665213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1334654</t>
+          <t>1335202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1345674</t>
+          <t>1344903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1008190</t>
+          <t>1006832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1019725</t>
+          <t>1019651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1027947</t>
+          <t>1027526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1039865</t>
+          <t>1039099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2041734</t>
+          <t>2040998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2057686</t>
+          <t>2057145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>753909</t>
+          <t>754124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>774569</t>
+          <t>775054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>784020</t>
+          <t>783927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1533119</t>
+          <t>1532951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1542582</t>
+          <t>1542681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926245</t>
+          <t>926619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936439</t>
+          <t>936449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1030760</t>
+          <t>1031312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1041962</t>
+          <t>1041961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1963788</t>
+          <t>1962394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1976797</t>
+          <t>1976813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3367878</t>
+          <t>3368356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3385308</t>
+          <t>3385464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3514635</t>
+          <t>3515659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3532727</t>
+          <t>3533076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6890955</t>
+          <t>6889779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6915835</t>
+          <t>6915046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>30294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26914</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>627599</t>
+          <t>681459</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619000</t>
+          <t>672975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631600</t>
+          <t>686255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>706258</t>
+          <t>714014</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>695746</t>
+          <t>703886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>713110</t>
+          <t>720725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1333858</t>
+          <t>1395473</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1322095</t>
+          <t>1381760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343050</t>
+          <t>1404710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22593</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35335</t>
+          <t>34634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>32329</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44172</t>
+          <t>44398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54455</t>
+          <t>56255</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71504</t>
+          <t>70655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1170271</t>
+          <t>1024991</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1157529</t>
+          <t>1014283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1182597</t>
+          <t>1033567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>926789</t>
+          <t>1039145</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>914479</t>
+          <t>1027076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935874</t>
+          <t>1048348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2097061</t>
+          <t>2064136</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2080012</t>
+          <t>2049736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2114936</t>
+          <t>2076848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>31672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11244</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>683719</t>
+          <t>782029</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670339</t>
+          <t>771401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>692148</t>
+          <t>791377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>922122</t>
+          <t>797119</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>914971</t>
+          <t>789020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>928567</t>
+          <t>802791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1605841</t>
+          <t>1579148</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1589658</t>
+          <t>1564387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1618567</t>
+          <t>1589386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>29119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51932</t>
+          <t>54698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,17 +7633,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48750</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>39359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64088</t>
+          <t>62981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>90353</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70321</t>
+          <t>74099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106489</t>
+          <t>108589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>888146</t>
+          <t>949475</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874899</t>
+          <t>935364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>899235</t>
+          <t>960943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1046182</t>
+          <t>1069275</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1030844</t>
+          <t>1056060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1058691</t>
+          <t>1079682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1934328</t>
+          <t>2018751</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1915274</t>
+          <t>2000515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951442</t>
+          <t>2035005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110563</t>
+          <t>116429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>100735</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>139588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>187093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3369735</t>
+          <t>3437955</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3349254</t>
+          <t>3416333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3392408</t>
+          <t>3455584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3601351</t>
+          <t>3619552</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3581015</t>
+          <t>3597366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3625316</t>
+          <t>3636219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6971086</t>
+          <t>7057507</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6937037</t>
+          <t>7023888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7001522</t>
+          <t>7082623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
